--- a/hardware/production/BOM.xlsx
+++ b/hardware/production/BOM.xlsx
@@ -389,7 +389,7 @@
     <t>U3</t>
   </si>
   <si>
-    <t>ULN2803A</t>
+    <t>TBD62783A</t>
   </si>
   <si>
     <t>Transistor_Array:TBD62783A</t>
@@ -398,7 +398,7 @@
     <t>Package_DIP:DIP-18_W7.62mm_Socket</t>
   </si>
   <si>
-    <t>https://www.reichelt.de/eight-darlington-arrays-dil-18-uln-2803a-p22085.html?&amp;nbc=1</t>
+    <t>http://toshiba.semicon-storage.com/info/docget.jsp?did=30523&amp;prodName=TBD62783APG</t>
   </si>
   <si>
     <t>U4</t>
